--- a/downloads/rentsafe-engine-evidence.xlsx
+++ b/downloads/rentsafe-engine-evidence.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence'!$A$1:$Q$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence'!$A$1:$Q$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q115"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -862,7 +862,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>measure.volume.change_pct.p</t>
+          <t>measure.volume.change_pct</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -872,15 +872,15 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chance of a volume gap this large between the two 12-month windows if month-to-month variation were all there is (permutation test on monthly row counts)</t>
+          <t>Change in the average month's row volume, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3689</v>
+        <v>66.44951140065146</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -892,10 +892,10 @@
         <v>3272</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>0.6644951140065146</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>93.90000000000001</v>
@@ -903,31 +903,35 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
+          <t>no change test was run: only 8 of the latest 12 months and 6 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April in any year</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>A 66.4% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 8 of the latest 12 months and 6 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, and April in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (May, June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3689</v>
+        <v>66.44951140065146</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "WITH m(_month) AS (VALUES ('2025-09'), ('2025-10'), ('2025-11'), ('2025-12'), ('2026-01'), ('2026-02'), ('2026-03'), ('2026-04'), ('2026-05'), ('2026-06'), ('2026-07'), ('2026-08')) SELECT COUNT(a._month) FROM m LEFT JOIN \"_northledger_measure_client_rentsafeto_evaluation_view\" a ON a._month = m._month GROUP BY m._month ORDER BY 1", "sql_b": "WITH m(_month) AS (VALUES ('2024-09'), ('2024-10'), ('2024-11'), ('2024-12'), ('2025-01'), ('2025-02'), ('2025-03'), ('2025-04'), ('2025-05'), ('2025-06'), ('2025-07'), ('2025-08')) SELECT COUNT(a._month) FROM m LEFT JOIN \"_northledger_measure_client_rentsafeto_evaluation_view\" a ON a._month = m._month GROUP BY m._month ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT 100.0 * (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2025-09' AND '2026-08') / (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2024-09' AND '2025-08') - 100.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>measure.volume.change_pct</t>
+          <t>measure.proactive_score.extreme_rows</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -937,15 +941,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Change in row volume, latest 12 months against the 12 before</t>
+          <t>Rows of proactive_score more than 10 robust standard deviations from its median (below 32.7 or above 151), over the 24 months compared: kept, and the change is also stated without them</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>66.44951140065146</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>count</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -957,46 +961,38 @@
         <v>3272</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6644951140065146</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>months treated as exchangeable in the test; each window holds every calendar month once, so seasonality is balanced</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>A 66% difference across 3,272 rows, but a gap this size would still turn up by chance in about 37 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>More of the same pattern: it has held for 5 periods so far, and another 2 periods at this size, or a pull wider than 3,272 rows, would separate a real difference from noise.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>66.44951140065146</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2025-09' AND '2026-08') / (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2024-09' AND '2025-08') - 100.0</t>
+          <t>SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' AND ("proactive_score" &lt; 32.696000000000005 OR "proactive_score" &gt; 151.304)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.mean</t>
+          <t>measure.proactive_score.extreme_rows.largest</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1006,11 +1002,11 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Average proactive_score over 2023-06 to 2026-08</t>
+          <t>The most extreme value of proactive_score over the 24 months compared</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>88.85512272367379</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -1023,7 +1019,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -1046,18 +1042,18 @@
         <v>1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>88.85512272367379</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT "proactive_score" FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' ORDER BY ABS("proactive_score" - 92.0) DESC LIMIT 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.median</t>
+          <t>measure.proactive_score.median24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1067,11 +1063,11 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Median proactive_score over 2023-06 to 2026-08</t>
+          <t>Median proactive_score over the 24 months compared</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -1084,7 +1080,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
@@ -1107,18 +1103,18 @@
         <v>1</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "proactive_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT AVG(v) FROM (SELECT "proactive_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.last12_mean</t>
+          <t>measure.proactive_score.last12_median</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1128,11 +1124,11 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Average proactive_score in the latest 12 months</t>
+          <t>Median proactive_score in the latest 12 months</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>90.43737769080235</v>
+        <v>92</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1168,18 +1164,18 @@
         <v>1</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>90.43737769080235</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "proactive_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.prior12_mean</t>
+          <t>measure.proactive_score.prior12_median</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1189,11 +1185,11 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Average proactive_score in the 12 months before</t>
+          <t>Median proactive_score in the 12 months before</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>89.66775244299674</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -1229,18 +1225,18 @@
         <v>1</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>89.66775244299674</v>
+        <v>92</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "proactive_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.change.p</t>
+          <t>measure.current_score.extreme_rows</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1250,15 +1246,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average proactive_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Rows of current_score more than 10 robust standard deviations from its median (below 32.7 or above 151), over the 24 months compared: kept, and the change is also stated without them</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.0059</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>count</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1279,11 +1275,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -1294,18 +1286,18 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.0059</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"proactive_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"proactive_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"proactive_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"proactive_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' AND ("current_score" &lt; 32.696000000000005 OR "current_score" &gt; 151.304)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>measure.proactive_score.change</t>
+          <t>measure.current_score.extreme_rows.largest</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1315,15 +1307,15 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Change in average proactive_score, latest 12 months against the 12 before</t>
+          <t>The most extreme value of current_score over the 24 months compared</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.7696252478056067</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>proactive_score</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1335,10 +1327,10 @@
         <v>3272</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.008583077269555407</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>93.90000000000001</v>
@@ -1347,30 +1339,26 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 0.8% where we want at least 5% before changing anything.</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.7696252478056067</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT "current_score" FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' ORDER BY ABS("current_score" - 92.0) DESC LIMIT 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.mean</t>
+          <t>measure.current_score.median24</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1380,11 +1368,11 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Average current_score over 2023-06 to 2026-08</t>
+          <t>Median current_score over the 24 months compared</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>88.76280285035629</v>
+        <v>92</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1385,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>
@@ -1420,18 +1408,18 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>88.76280285035629</v>
+        <v>92</v>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "current_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.median</t>
+          <t>measure.current_score.last12_median</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1441,11 +1429,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Median current_score over 2023-06 to 2026-08</t>
+          <t>Median current_score in the latest 12 months</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1458,7 +1446,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>0</v>
@@ -1481,18 +1469,18 @@
         <v>1</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "current_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT AVG(v) FROM (SELECT "current_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.last12_mean</t>
+          <t>measure.current_score.prior12_median</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1502,11 +1490,11 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Average current_score in the latest 12 months</t>
+          <t>Median current_score in the 12 months before</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>90.23140900195695</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1542,18 +1530,18 @@
         <v>1</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>90.23140900195695</v>
+        <v>91</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "current_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.prior12_mean</t>
+          <t>measure.refused_items.total.last12</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1563,15 +1551,15 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Average current_score in the 12 months before</t>
+          <t>Total refused_items in the latest 12 months (2025-09 to 2026-08)</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>89.57654723127035</v>
+        <v>341</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>current_score</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1603,18 +1591,18 @@
         <v>1</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>89.57654723127035</v>
+        <v>341</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT SUM("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.change.p</t>
+          <t>measure.refused_items.total.prior12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1624,15 +1612,15 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average current_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Total refused_items in the 12 months before (2024-09 to 2025-08)</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.0209</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1653,11 +1641,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -1668,18 +1652,18 @@
         <v>1</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.0209</v>
+        <v>202</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"current_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"current_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"current_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"current_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT SUM("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>measure.current_score.change</t>
+          <t>measure.refused_items.total.change</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1689,15 +1673,15 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Change in average current_score, latest 12 months against the 12 before</t>
+          <t>Change in the monthly total of refused_items, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.654861770686594</v>
+        <v>68.8118811881188</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>current_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1709,42 +1693,46 @@
         <v>3272</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.007310638676392159</v>
+        <v>0.6881188118811881</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>no change test was run: only 6 of the latest 12 months and 6 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 0.7% where we want at least 5% before changing anything.</t>
+          <t>A 68.8% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 6 of the latest 12 months and 6 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
         </is>
       </c>
       <c r="O20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.654861770686594</v>
+        <v>68.8118811881188</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT 100.0 * (SELECT SUM("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') / (SELECT SUM("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08') - 100.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.mean</t>
+          <t>measure.proactive_score.mean</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1754,15 +1742,15 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Average envelope_score over 2023-06 to 2026-08</t>
+          <t>Average proactive_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>85.03742517814726</v>
+        <v>88.85512272367379</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>envelope_score</t>
+          <t>proactive_score</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1794,18 +1782,18 @@
         <v>1</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>85.03742517814726</v>
+        <v>88.85512272367379</v>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.median</t>
+          <t>measure.proactive_score.median</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1815,15 +1803,15 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Median envelope_score over 2023-06 to 2026-08</t>
+          <t>Median proactive_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>86.67</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>envelope_score</t>
+          <t>proactive_score</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1855,18 +1843,18 @@
         <v>1</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>86.67</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "envelope_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT AVG(v) FROM (SELECT "proactive_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.last12_mean</t>
+          <t>measure.proactive_score.last12_mean</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1876,15 +1864,15 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Average envelope_score in the latest 12 months</t>
+          <t>Average month of proactive_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>85.94915362035225</v>
+        <v>90.30302175264423</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>envelope_score</t>
+          <t>proactive_score</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1916,18 +1904,18 @@
         <v>1</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>85.94915362035225</v>
+        <v>90.30302175264423</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.prior12_mean</t>
+          <t>measure.proactive_score.prior12_mean</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1937,15 +1925,15 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Average envelope_score in the 12 months before</t>
+          <t>Average month of proactive_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>86.16160423452769</v>
+        <v>89.64196409188959</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>envelope_score</t>
+          <t>proactive_score</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1977,18 +1965,18 @@
         <v>1</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>86.16160423452769</v>
+        <v>89.64196409188959</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.change.p</t>
+          <t>measure.proactive_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1998,15 +1986,15 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average envelope_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Change in the row-weighted average proactive_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.6377</v>
+        <v>0.7696252478056067</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>proactive_score</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2027,11 +2015,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -2042,18 +2026,18 @@
         <v>1</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.6377</v>
+        <v>0.7696252478056067</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"envelope_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"envelope_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"envelope_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"envelope_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT (SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("proactive_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>measure.envelope_score.change</t>
+          <t>measure.proactive_score.change</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2063,15 +2047,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Change in average envelope_score, latest 12 months against the 12 before</t>
+          <t>Change in the average month of proactive_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-0.2124506141754381</v>
+        <v>0.7374421873186634</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>envelope_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2083,42 +2067,46 @@
         <v>3272</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>-0.002465722592596557</v>
+        <v>0.007374421873186634</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of proactive_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>A 0.2% difference across 3,272 rows, but a gap this size would still turn up by chance in about 64 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
+          <t>A 0.7% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>More of the same pattern: it has held for 4 periods so far, and another 2 periods at this size, or a pull wider than 3,272 rows, would separate a real difference from noise.</t>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
         </is>
       </c>
       <c r="O26" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>-0.2124506141754381</v>
+        <v>0.7374421873186634</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.mean</t>
+          <t>measure.proactive_score.change_without_extremes</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2128,15 +2116,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Average grounds_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of proactive_score without its extreme rows, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>88.60941726049089</v>
+        <v>0.7873173897448709</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>grounds_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2145,7 +2133,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -2168,18 +2156,18 @@
         <v>1</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>88.60941726049089</v>
+        <v>0.7873173897448709</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' AND NOT ("proactive_score" &lt; 32.696000000000005 OR "proactive_score" &gt; 151.304) GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("proactive_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "proactive_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' AND NOT ("proactive_score" &lt; 32.696000000000005 OR "proactive_score" &gt; 151.304) GROUP BY _month HAVING COUNT("proactive_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.median</t>
+          <t>measure.current_score.mean</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2189,15 +2177,15 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Median grounds_score over 2023-06 to 2026-08</t>
+          <t>Average current_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>90</v>
+        <v>88.76280285035629</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>grounds_score</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2229,18 +2217,18 @@
         <v>1</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>90</v>
+        <v>88.76280285035629</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "grounds_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.last12_mean</t>
+          <t>measure.current_score.median</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2250,15 +2238,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Average grounds_score in the latest 12 months</t>
+          <t>Median current_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>89.6394324853229</v>
+        <v>91</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>grounds_score</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2267,7 +2255,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
@@ -2290,18 +2278,18 @@
         <v>1</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>89.6394324853229</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "current_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.prior12_mean</t>
+          <t>measure.current_score.last12_mean</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2311,15 +2299,15 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Average grounds_score in the 12 months before</t>
+          <t>Average month of current_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>88.44848534201955</v>
+        <v>90.10193365646056</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>grounds_score</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2351,18 +2339,18 @@
         <v>1</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>88.44848534201955</v>
+        <v>90.10193365646056</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("current_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.change.p</t>
+          <t>measure.current_score.prior12_mean</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2372,15 +2360,15 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average grounds_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of current_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.0014</v>
+        <v>89.52537298520448</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2401,11 +2389,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -2416,18 +2400,18 @@
         <v>1</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.0014</v>
+        <v>89.52537298520448</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"grounds_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"grounds_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"grounds_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"grounds_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("current_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>measure.grounds_score.change</t>
+          <t>measure.current_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2437,15 +2421,15 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Change in average grounds_score, latest 12 months against the 12 before</t>
+          <t>Change in the row-weighted average current_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.190947143303347</v>
+        <v>0.654861770686594</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>grounds_score</t>
+          <t>current_score</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2457,10 +2441,10 @@
         <v>3272</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.0134648675858959</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>93.90000000000001</v>
@@ -2469,30 +2453,26 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 1.3% where we want at least 5% before changing anything.</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1.190947143303347</v>
+        <v>0.654861770686594</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT (SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("current_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.mean</t>
+          <t>measure.current_score.change</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2502,15 +2482,15 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Average entry_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of current_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>94.09989390340459</v>
+        <v>0.644019289761971</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>entry_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2519,41 +2499,49 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0</v>
+        <v>0.006440192897619709</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of current_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>A 0.6% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>94.09989390340459</v>
+        <v>0.644019289761971</v>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("current_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("current_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.median</t>
+          <t>measure.current_score.change_without_extremes</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2563,15 +2551,15 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Median entry_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of current_score without its extreme rows, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>100</v>
+        <v>0.6937710700531312</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>entry_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2580,7 +2568,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -2603,18 +2591,18 @@
         <v>1</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>100</v>
+        <v>0.6937710700531312</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "entry_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' AND NOT ("current_score" &lt; 32.696000000000005 OR "current_score" &gt; 151.304) GROUP BY _month HAVING COUNT("current_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("current_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "current_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' AND NOT ("current_score" &lt; 32.696000000000005 OR "current_score" &gt; 151.304) GROUP BY _month HAVING COUNT("current_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.last12_mean</t>
+          <t>measure.envelope_score.mean</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2624,15 +2612,15 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Average entry_score in the latest 12 months</t>
+          <t>Average envelope_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>94.83334637964774</v>
+        <v>85.03742517814726</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>entry_score</t>
+          <t>envelope_score</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2641,7 +2629,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -2664,18 +2652,18 @@
         <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>94.83334637964774</v>
+        <v>85.03742517814726</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.prior12_mean</t>
+          <t>measure.envelope_score.median</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2685,15 +2673,15 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Average entry_score in the 12 months before</t>
+          <t>Median envelope_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>94.80377850162866</v>
+        <v>86.67</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>entry_score</t>
+          <t>envelope_score</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2702,7 +2690,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>0</v>
@@ -2725,18 +2713,18 @@
         <v>1</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>94.80377850162866</v>
+        <v>86.67</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "envelope_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.change.p</t>
+          <t>measure.envelope_score.last12_mean</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2746,15 +2734,15 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average entry_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of envelope_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.9219000000000001</v>
+        <v>86.10911451656969</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>envelope_score</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2775,11 +2763,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -2790,18 +2774,18 @@
         <v>1</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>0.9219000000000001</v>
+        <v>86.10911451656969</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"entry_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"entry_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"entry_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"entry_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("envelope_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("envelope_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>measure.entry_score.change</t>
+          <t>measure.envelope_score.prior12_mean</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2811,15 +2795,15 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Change in average entry_score, latest 12 months against the 12 before</t>
+          <t>Average month of envelope_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.02956787801907979</v>
+        <v>87.17047341295441</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>entry_score</t>
+          <t>envelope_score</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2831,10 +2815,10 @@
         <v>3272</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.0003118850164666362</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>93.90000000000001</v>
@@ -2843,30 +2827,26 @@
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>A 0% difference across 3,272 rows, but a gap this size would still turn up by chance in about 92 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>More of the same pattern: it has held for 2 periods so far, and another 2 periods at this size, or a pull wider than 3,272 rows, would separate a real difference from noise.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.02956787801907979</v>
+        <v>87.17047341295441</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("envelope_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("envelope_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.mean</t>
+          <t>measure.envelope_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2876,15 +2856,15 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Average systems_score over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average envelope_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>94.08193809523809</v>
+        <v>-0.2124506141754381</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>systems_score</t>
+          <t>envelope_score</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2893,7 +2873,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -2916,18 +2896,18 @@
         <v>1</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>94.08193809523809</v>
+        <v>-0.2124506141754381</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("envelope_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.median</t>
+          <t>measure.envelope_score.change</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2937,15 +2917,15 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Median systems_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of envelope_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>100</v>
+        <v>-1.217566975180588</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>systems_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2954,41 +2934,49 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0</v>
+        <v>-0.01217566975180588</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of envelope_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>A 1.2% fall in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>100</v>
+        <v>-1.217566975180588</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "systems_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("envelope_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("envelope_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("envelope_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "envelope_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("envelope_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.last12_mean</t>
+          <t>measure.grounds_score.mean</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2998,15 +2986,15 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Average systems_score in the latest 12 months</t>
+          <t>Average grounds_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>94.49414992650661</v>
+        <v>88.60941726049089</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>systems_score</t>
+          <t>grounds_score</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3015,7 +3003,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -3038,18 +3026,18 @@
         <v>1</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>94.49414992650661</v>
+        <v>88.60941726049089</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.prior12_mean</t>
+          <t>measure.grounds_score.median</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3059,15 +3047,15 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Average systems_score in the 12 months before</t>
+          <t>Median grounds_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>94.38641401792991</v>
+        <v>90</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>systems_score</t>
+          <t>grounds_score</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3076,7 +3064,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>0</v>
@@ -3099,18 +3087,18 @@
         <v>1</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>94.38641401792991</v>
+        <v>90</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "grounds_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.change.p</t>
+          <t>measure.grounds_score.last12_mean</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3120,15 +3108,15 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average systems_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of grounds_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.7567</v>
+        <v>89.66574260231485</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>grounds_score</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3137,7 +3125,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3268</v>
+        <v>3272</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>0</v>
@@ -3149,11 +3137,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -3164,18 +3148,18 @@
         <v>1</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.7567</v>
+        <v>89.66574260231485</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"systems_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"systems_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"systems_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"systems_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("grounds_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("grounds_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>measure.systems_score.change</t>
+          <t>measure.grounds_score.prior12_mean</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3185,15 +3169,15 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Change in average systems_score, latest 12 months against the 12 before</t>
+          <t>Average month of grounds_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.1077359085767</v>
+        <v>88.62939277768798</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>systems_score</t>
+          <t>grounds_score</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3202,13 +3186,13 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3268</v>
+        <v>3272</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.001141434492428478</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>93.90000000000001</v>
@@ -3217,30 +3201,26 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>A 0.1% difference across 3,268 rows, but a gap this size would still turn up by chance in about 76 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>More of the same pattern: it has held for 4 periods so far, and another 2 periods at this size, or a pull wider than 3,268 rows, would separate a real difference from noise.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.1077359085767</v>
+        <v>88.62939277768798</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("grounds_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("grounds_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.mean</t>
+          <t>measure.grounds_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3250,15 +3230,15 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Average stairs_score over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average grounds_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>85.54734295685279</v>
+        <v>1.190947143303347</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>stairs_score</t>
+          <t>grounds_score</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3267,7 +3247,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0</v>
@@ -3290,18 +3270,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>85.54734295685279</v>
+        <v>1.190947143303347</v>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("grounds_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.median</t>
+          <t>measure.grounds_score.change</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3311,15 +3291,15 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Median stairs_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of grounds_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>87.3</v>
+        <v>1.169307147603263</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>stairs_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3328,41 +3308,49 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>0.01169307147603263</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of grounds_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>A 1.2% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>87.3</v>
+        <v>1.169307147603263</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "stairs_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("grounds_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("grounds_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("grounds_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "grounds_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("grounds_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.last12_mean</t>
+          <t>measure.entry_score.mean</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3372,15 +3360,15 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Average stairs_score in the latest 12 months</t>
+          <t>Average entry_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>87.61297257590597</v>
+        <v>94.09989390340459</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>stairs_score</t>
+          <t>entry_score</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3389,7 +3377,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0</v>
@@ -3412,18 +3400,18 @@
         <v>1</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>87.61297257590597</v>
+        <v>94.09989390340459</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.prior12_mean</t>
+          <t>measure.entry_score.median</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3433,15 +3421,15 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Average stairs_score in the 12 months before</t>
+          <t>Median entry_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>85.64021189894051</v>
+        <v>100</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>stairs_score</t>
+          <t>entry_score</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3450,7 +3438,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>0</v>
@@ -3473,18 +3461,18 @@
         <v>1</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>85.64021189894051</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "entry_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.change.p</t>
+          <t>measure.entry_score.last12_mean</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3494,15 +3482,15 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average stairs_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of entry_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.0001</v>
+        <v>94.50377156014967</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>entry_score</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3511,7 +3499,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>0</v>
@@ -3523,11 +3511,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -3538,18 +3522,18 @@
         <v>1</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.0001</v>
+        <v>94.50377156014967</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"stairs_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"stairs_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"stairs_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"stairs_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("entry_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("entry_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>measure.stairs_score.change</t>
+          <t>measure.entry_score.prior12_mean</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3559,15 +3543,15 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Change in average stairs_score, latest 12 months against the 12 before</t>
+          <t>Average month of entry_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.972760676965464</v>
+        <v>94.63201543634162</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>stairs_score</t>
+          <t>entry_score</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3576,13 +3560,13 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.02303544833930835</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>93.90000000000001</v>
@@ -3591,30 +3575,26 @@
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 2.3% where we want at least 5% before changing anything.</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1.972760676965464</v>
+        <v>94.63201543634162</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("entry_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("entry_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.mean</t>
+          <t>measure.entry_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3624,15 +3604,15 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Average interiors_score over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average entry_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>87.66551172370089</v>
+        <v>0.02956787801907979</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>interiors_score</t>
+          <t>entry_score</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3641,7 +3621,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
@@ -3664,18 +3644,18 @@
         <v>1</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>87.66551172370089</v>
+        <v>0.02956787801907979</v>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("entry_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.median</t>
+          <t>measure.entry_score.change</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3685,15 +3665,15 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Median interiors_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of entry_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>90.91</v>
+        <v>-0.1355184876921669</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>interiors_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3702,41 +3682,49 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>-0.001355184876921669</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of entry_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>A 0.1% fall in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>90.91</v>
+        <v>-0.1355184876921669</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "interiors_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("entry_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("entry_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("entry_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "entry_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("entry_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.last12_mean</t>
+          <t>measure.systems_score.mean</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3746,15 +3734,15 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Average interiors_score in the latest 12 months</t>
+          <t>Average systems_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>89.31795499021526</v>
+        <v>94.08193809523809</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>interiors_score</t>
+          <t>systems_score</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3763,7 +3751,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
@@ -3786,18 +3774,18 @@
         <v>1</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>89.31795499021526</v>
+        <v>94.08193809523809</v>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.prior12_mean</t>
+          <t>measure.systems_score.median</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3807,15 +3795,15 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Average interiors_score in the 12 months before</t>
+          <t>Median systems_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>88.53244299674267</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>interiors_score</t>
+          <t>systems_score</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3824,7 +3812,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -3847,18 +3835,18 @@
         <v>1</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>88.53244299674267</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "systems_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.change.p</t>
+          <t>measure.systems_score.last12_mean</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3868,15 +3856,15 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average interiors_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of systems_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.0774</v>
+        <v>94.23476588272153</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>systems_score</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3897,11 +3885,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -3912,18 +3896,18 @@
         <v>1</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>0.0774</v>
+        <v>94.23476588272153</v>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"interiors_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"interiors_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"interiors_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"interiors_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("systems_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("systems_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>measure.interiors_score.change</t>
+          <t>measure.systems_score.prior12_mean</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3933,15 +3917,15 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Change in average interiors_score, latest 12 months against the 12 before</t>
+          <t>Average month of systems_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.785511993472582</v>
+        <v>94.17576942724126</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>interiors_score</t>
+          <t>systems_score</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3953,10 +3937,10 @@
         <v>3272</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.008872589153577101</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>93.90000000000001</v>
@@ -3965,30 +3949,26 @@
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>A 0.8% difference across 3,272 rows, but a gap this size would still turn up by chance in about 8 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>More of the same pattern: it has held for 5 periods so far, and another 2 periods at this size, or a pull wider than 3,272 rows, would separate a real difference from noise.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>0.785511993472582</v>
+        <v>94.17576942724126</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("systems_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("systems_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.mean</t>
+          <t>measure.systems_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3998,15 +3978,15 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Average waste_score over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average systems_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>91.96218032007604</v>
+        <v>0.1077359085767</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>waste_score</t>
+          <t>systems_score</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4015,7 +3995,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6681</v>
+        <v>3268</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
@@ -4038,18 +4018,18 @@
         <v>1</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>91.96218032007604</v>
+        <v>0.1077359085767</v>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("systems_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.median</t>
+          <t>measure.systems_score.change</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4059,15 +4039,15 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Median waste_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of systems_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>96.97</v>
+        <v>0.06264504748840238</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>waste_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4076,41 +4056,49 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>6681</v>
+        <v>3268</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0</v>
+        <v>0.0006264504748840238</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of systems_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>A 0.1% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>96.97</v>
+        <v>0.06264504748840238</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "waste_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("systems_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("systems_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("systems_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "systems_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("systems_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.last12_mean</t>
+          <t>measure.stairs_score.mean</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4120,15 +4108,15 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Average waste_score in the latest 12 months</t>
+          <t>Average stairs_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>93.40055854973053</v>
+        <v>85.54734295685279</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>waste_score</t>
+          <t>stairs_score</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4137,7 +4125,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>0</v>
@@ -4160,18 +4148,18 @@
         <v>1</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>93.40055854973053</v>
+        <v>85.54734295685279</v>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.prior12_mean</t>
+          <t>measure.stairs_score.median</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4181,15 +4169,15 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Average waste_score in the 12 months before</t>
+          <t>Median stairs_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>92.15139250814333</v>
+        <v>87.3</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>waste_score</t>
+          <t>stairs_score</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4198,7 +4186,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>0</v>
@@ -4221,18 +4209,18 @@
         <v>1</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>92.15139250814333</v>
+        <v>87.3</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "stairs_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.change.p</t>
+          <t>measure.stairs_score.last12_mean</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4242,15 +4230,15 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average waste_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of stairs_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.0011</v>
+        <v>87.37902652806721</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>stairs_score</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4259,7 +4247,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>0</v>
@@ -4271,11 +4259,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -4286,18 +4270,18 @@
         <v>1</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>0.0011</v>
+        <v>87.37902652806721</v>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"waste_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"waste_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"waste_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"waste_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("stairs_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("stairs_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>measure.waste_score.change</t>
+          <t>measure.stairs_score.prior12_mean</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4307,15 +4291,15 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Change in average waste_score, latest 12 months against the 12 before</t>
+          <t>Average month of stairs_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.249166041587202</v>
+        <v>86.21442829672648</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>waste_score</t>
+          <t>stairs_score</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4324,13 +4308,13 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.01355558508219845</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>93.90000000000001</v>
@@ -4339,30 +4323,26 @@
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 1.3% where we want at least 5% before changing anything.</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>1.249166041587202</v>
+        <v>86.21442829672648</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("stairs_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("stairs_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.mean</t>
+          <t>measure.stairs_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4372,15 +4352,15 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Average paperwork_score over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average stairs_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>88.11464439140812</v>
+        <v>1.972760676965464</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>paperwork_score</t>
+          <t>stairs_score</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4389,7 +4369,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>6681</v>
+        <v>3269</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>0</v>
@@ -4412,18 +4392,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>88.11464439140812</v>
+        <v>1.972760676965464</v>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("stairs_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.median</t>
+          <t>measure.stairs_score.change</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4433,15 +4413,15 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Median paperwork_score over 2023-06 to 2026-08</t>
+          <t>Change in the average month of stairs_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>100</v>
+        <v>1.350815929942144</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>paperwork_score</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4450,41 +4430,49 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>6681</v>
+        <v>3269</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0</v>
+        <v>0.01350815929942144</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of stairs_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>A 1.4% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>100</v>
+        <v>1.350815929942144</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "paperwork_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("stairs_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("stairs_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("stairs_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "stairs_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("stairs_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.last12_mean</t>
+          <t>measure.interiors_score.mean</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4494,15 +4482,15 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Average paperwork_score in the latest 12 months</t>
+          <t>Average interiors_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>92.59627085377822</v>
+        <v>87.66551172370089</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>paperwork_score</t>
+          <t>interiors_score</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4511,7 +4499,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>0</v>
@@ -4534,18 +4522,18 @@
         <v>1</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>92.59627085377822</v>
+        <v>87.66551172370089</v>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.prior12_mean</t>
+          <t>measure.interiors_score.median</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4555,15 +4543,15 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Average paperwork_score in the 12 months before</t>
+          <t>Median interiors_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>90.31093213409649</v>
+        <v>90.91</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>paperwork_score</t>
+          <t>interiors_score</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4572,7 +4560,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>0</v>
@@ -4595,18 +4583,18 @@
         <v>1</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>90.31093213409649</v>
+        <v>90.91</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "interiors_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.change.p</t>
+          <t>measure.interiors_score.last12_mean</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4616,15 +4604,15 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average paperwork_score between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of interiors_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.0001</v>
+        <v>88.81422473841141</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>interiors_score</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4633,7 +4621,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>3261</v>
+        <v>3272</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
@@ -4645,11 +4633,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -4660,18 +4644,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>0.0001</v>
+        <v>88.81422473841141</v>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"paperwork_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"paperwork_score\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"paperwork_score\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"paperwork_score\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("interiors_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("interiors_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>measure.paperwork_score.change</t>
+          <t>measure.interiors_score.prior12_mean</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4681,15 +4665,15 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Change in average paperwork_score, latest 12 months against the 12 before</t>
+          <t>Average month of interiors_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.285338719681732</v>
+        <v>88.42457078869825</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>paperwork_score</t>
+          <t>interiors_score</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4698,13 +4682,13 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>3261</v>
+        <v>3272</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.02530522790184903</v>
+        <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>93.90000000000001</v>
@@ -4713,30 +4697,26 @@
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Solid enough to keep an eye on, not enough to act on: the difference is 2.5% where we want at least 5% before changing anything.</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>To turn this into a recommendation: the gap would have to widen to about 5%.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>2.285338719681732</v>
+        <v>88.42457078869825</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("interiors_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("interiors_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.mean</t>
+          <t>measure.interiors_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4746,15 +4726,15 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Average refused_items over 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average interiors_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.2359461599366587</v>
+        <v>0.785511993472582</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>refused_items</t>
+          <t>interiors_score</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4763,7 +4743,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
@@ -4786,18 +4766,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.2359461599366587</v>
+        <v>0.785511993472582</v>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("interiors_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.median</t>
+          <t>measure.interiors_score.change</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4807,15 +4787,15 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Median refused_items over 2023-06 to 2026-08</t>
+          <t>Change in the average month of interiors_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0</v>
+        <v>0.4406625287945047</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>refused_items</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4824,41 +4804,49 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0</v>
+        <v>0.004406625287945047</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of interiors_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>A 0.4% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0</v>
+        <v>0.4406625287945047</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(v) FROM (SELECT "refused_items" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("interiors_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("interiors_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("interiors_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "interiors_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("interiors_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.last12_mean</t>
+          <t>measure.waste_score.mean</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4868,15 +4856,15 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Average refused_items in the latest 12 months</t>
+          <t>Average waste_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.1668297455968689</v>
+        <v>91.96218032007604</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>refused_items</t>
+          <t>waste_score</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4885,7 +4873,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>0</v>
@@ -4908,18 +4896,18 @@
         <v>1</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>0.1668297455968689</v>
+        <v>91.96218032007604</v>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08'</t>
+          <t>SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.prior12_mean</t>
+          <t>measure.waste_score.median</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4929,15 +4917,15 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Average refused_items in the 12 months before</t>
+          <t>Median waste_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.1644951140065146</v>
+        <v>96.97</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>refused_items</t>
+          <t>waste_score</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4946,7 +4934,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3272</v>
+        <v>6681</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>0</v>
@@ -4969,18 +4957,18 @@
         <v>1</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>0.1644951140065146</v>
+        <v>96.97</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "waste_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.change.p</t>
+          <t>measure.waste_score.last12_mean</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4990,15 +4978,15 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Chance of a gap this large in average refused_items between the two 12-month windows if the windows did not differ (permutation test on every row)</t>
+          <t>Average month of waste_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.9695</v>
+        <v>93.62925469130231</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>waste_score</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -5019,11 +5007,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>9999 shuffles, seed 20260923, two-sided</t>
-        </is>
-      </c>
+      <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
@@ -5034,18 +5018,18 @@
         <v>1</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>0.9695</v>
+        <v>93.62925469130231</v>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>{"kind": "northledger.permutation/1", "n_perm": 9999, "seed": 20260923, "sided": "two", "sql_a": "SELECT \"refused_items\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' ORDER BY 1", "sql_b": "SELECT \"refused_items\" FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' ORDER BY 1", "stat": "mean_difference"}</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("waste_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("waste_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>measure.refused_items.change</t>
+          <t>measure.waste_score.prior12_mean</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5055,15 +5039,15 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Change in average refused_items, latest 12 months against the 12 before</t>
+          <t>Average month of waste_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.002334631590354241</v>
+        <v>91.59889493725998</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>refused_items</t>
+          <t>waste_score</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5075,10 +5059,10 @@
         <v>3272</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.01419271085621291</v>
+        <v>0</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>93.90000000000001</v>
@@ -5087,30 +5071,26 @@
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>A 1.4% difference across 3,272 rows, but a gap this size would still turn up by chance in about 97 of 100 similar datasets -- we only call something settled at 5 in 100 or better. Worth tracking, not worth acting on yet.</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>More of the same pattern: it has held for 4 periods so far, and another 2 periods at this size, or a pull wider than 3,272 rows, would separate a real difference from noise.</t>
-        </is>
-      </c>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.002334631590354241</v>
+        <v>91.59889493725998</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>SELECT (SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("waste_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("waste_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>measure.ward_name.share.1</t>
+          <t>measure.waste_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5120,15 +5100,15 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where ward_name is 'Toronto-St. Paul's' (rank 1 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average waste_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.675376088677751</v>
+        <v>1.249166041587202</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>waste_score</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5137,7 +5117,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>6681</v>
+        <v>3269</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>0</v>
@@ -5160,18 +5140,18 @@
         <v>1</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>9.675376088677751</v>
+        <v>1.249166041587202</v>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Toronto-St. Paul''s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("waste_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>measure.ward_name.share.2</t>
+          <t>measure.waste_score.change</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5181,11 +5161,11 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where ward_name is 'Etobicoke-Lakeshore' (rank 2 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the average month of waste_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>6.967537608867775</v>
+        <v>2.216576690617288</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -5198,41 +5178,49 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>6681</v>
+        <v>3269</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0</v>
+        <v>0.02216576690617288</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of waste_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>A 2.2% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>6.967537608867775</v>
+        <v>2.216576690617288</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Etobicoke-Lakeshore' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("waste_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("waste_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("waste_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "waste_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("waste_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>measure.ward_name.share.3</t>
+          <t>measure.paperwork_score.mean</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5242,15 +5230,15 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where ward_name is 'York South-Weston' (rank 3 by rows), 2023-06 to 2026-08</t>
+          <t>Average paperwork_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>6.951702296120349</v>
+        <v>88.11464439140812</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>paperwork_score</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5282,18 +5270,18 @@
         <v>1</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>6.951702296120349</v>
+        <v>88.11464439140812</v>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'York South-Weston' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>measure.ward_name.share.4</t>
+          <t>measure.paperwork_score.median</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5303,15 +5291,15 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where ward_name is 'Eglinton-Lawrence' (rank 4 by rows), 2023-06 to 2026-08</t>
+          <t>Median paperwork_score over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6.920031670625495</v>
+        <v>100</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>paperwork_score</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5343,18 +5331,18 @@
         <v>1</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>6.920031670625495</v>
+        <v>100</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Eglinton-Lawrence' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "paperwork_score" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>measure.ward_name.share.5</t>
+          <t>measure.paperwork_score.last12_mean</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5364,15 +5352,15 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where ward_name is 'York Centre' (rank 5 by rows), 2023-06 to 2026-08</t>
+          <t>Average month of paperwork_score in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6.619160728424387</v>
+        <v>92.70710786389876</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>paperwork_score</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5381,7 +5369,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>0</v>
@@ -5404,18 +5392,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>6.619160728424387</v>
+        <v>92.70710786389876</v>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'York Centre' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("paperwork_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("paperwork_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>measure.district.share.1</t>
+          <t>measure.paperwork_score.prior12_mean</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5425,15 +5413,15 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where district is 'Toronto and East York' (rank 1 by rows), 2023-06 to 2026-08</t>
+          <t>Average month of paperwork_score in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>39.74663499604117</v>
+        <v>90.09300324173496</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>paperwork_score</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -5442,7 +5430,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0</v>
@@ -5465,18 +5453,18 @@
         <v>1</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>39.74663499604117</v>
+        <v>90.09300324173496</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Toronto and East York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("paperwork_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("paperwork_score") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>measure.district.share.2</t>
+          <t>measure.paperwork_score.change_row_weighted</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5486,15 +5474,15 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where district is 'North York' (rank 2 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average paperwork_score, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>25.68487727632621</v>
+        <v>2.285338719681732</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>paperwork_score</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5503,7 +5491,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>6681</v>
+        <v>3261</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>0</v>
@@ -5526,18 +5514,18 @@
         <v>1</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>25.68487727632621</v>
+        <v>2.285338719681732</v>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'North York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("paperwork_score") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>measure.district.share.3</t>
+          <t>measure.paperwork_score.change</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5547,11 +5535,11 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where district is 'Etobicoke York' (rank 3 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the average month of paperwork_score, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>22.18527315914489</v>
+        <v>2.901562305731673</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -5564,41 +5552,49 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>6681</v>
+        <v>3261</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0</v>
+        <v>0.02901562305731673</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>3 months with fewer than 15 rows of paperwork_score (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row); no change test was run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>A 2.9% rise in the average month, latest 12 months against the 12 before, but no change test could be run: only 7 of the latest 12 months and 5 of the 12 before hold a usable value; the test needs at least 10 in each; the file holds no values for January, February, March, April, May in any year. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>This file holds no values for January, February, March, April, and May in any year, so a comparison of every month cannot run on this collection pattern, and waiting will not change that. What would settle it is comparing only the months that are sampled (June, July, August, September, October, November, and December) year against year, which this release does not run.</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>22.18527315914489</v>
+        <v>2.901562305731673</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Etobicoke York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * (SELECT AVG(v) FROM (SELECT AVG("paperwork_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("paperwork_score") &gt;= 15)) / (SELECT AVG(v) FROM (SELECT AVG("paperwork_score") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "paperwork_score" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("paperwork_score") &gt;= 15)) - 100.0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>measure.district.share.4</t>
+          <t>measure.refused_items.mean</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5608,15 +5604,15 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where district is 'Scarborough' (rank 4 by rows), 2023-06 to 2026-08</t>
+          <t>Average refused_items over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>12.38321456848773</v>
+        <v>0.2359461599366587</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5648,18 +5644,18 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>12.38321456848773</v>
+        <v>0.2359461599366587</v>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Scarborough' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>measure.property_type.share.1</t>
+          <t>measure.refused_items.median</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5669,15 +5665,15 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where property_type is 'PRIVATE' (rank 1 by rows), 2023-06 to 2026-08</t>
+          <t>Median refused_items over 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>84.3230403800475</v>
+        <v>0</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5709,18 +5705,18 @@
         <v>1</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>84.3230403800475</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'PRIVATE' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT "refused_items" AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' ORDER BY v LIMIT 2 - (SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') % 2 OFFSET ((SELECT COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08') - 1) / 2)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>measure.property_type.share.2</t>
+          <t>measure.refused_items.last12_mean</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5730,15 +5726,15 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where property_type is 'TCHC' (rank 2 by rows), 2023-06 to 2026-08</t>
+          <t>Average month of refused_items in the latest 12 months (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9.105304829770388</v>
+        <v>0.1627818237437607</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5747,7 +5743,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>0</v>
@@ -5770,18 +5766,18 @@
         <v>1</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>9.105304829770388</v>
+        <v>0.1627818237437607</v>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'TCHC' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("refused_items") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("refused_items") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>measure.property_type.share.3</t>
+          <t>measure.refused_items.prior12_mean</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5791,15 +5787,15 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where property_type is 'SOCIAL HOUSING' (rank 3 by rows), 2023-06 to 2026-08</t>
+          <t>Average month of refused_items in the 12 months before (the mean of the monthly averages)</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6.571654790182106</v>
+        <v>0.3378767294956927</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5808,7 +5804,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>0</v>
@@ -5831,18 +5827,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>6.571654790182106</v>
+        <v>0.3378767294956927</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'SOCIAL HOUSING' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT AVG(v) FROM (SELECT AVG("refused_items") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("refused_items") &gt;= 15)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>measure.decade_built.share.1</t>
+          <t>measure.refused_items.change_row_weighted</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5852,15 +5848,15 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where decade_built is '1960s' (rank 1 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the row-weighted average refused_items, latest 12 months against the 12 before (descriptive: every row counts once, so busy months weigh more; not the tested change)</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>33.34916864608076</v>
+        <v>0.002334631590354241</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5869,7 +5865,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>0</v>
@@ -5892,18 +5888,18 @@
         <v>1</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>33.34916864608076</v>
+        <v>0.002334631590354241</v>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1960s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08') - (SELECT AVG("refused_items") FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08')</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>measure.decade_built.share.2</t>
+          <t>measure.refused_items.change</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5913,15 +5909,15 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where decade_built is '1950s' (rank 2 by rows), 2023-06 to 2026-08</t>
+          <t>Change in the average month of refused_items, latest 12 months against the 12 before</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>26.41330166270784</v>
+        <v>-0.175094905751932</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>refused_items</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5930,41 +5926,49 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>6681</v>
+        <v>3272</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0</v>
+        <v>-0.518221263752833</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>some of its monthly averages in the two compared windows are at or below zero (they cross zero), so the change has no ratio and is stated in the measure's own units; no change test was run; 3 months with fewer than 15 rows of refused_items (under 5% of the median month) are left out of the change as gaps: 2023-12 (2 rows), 2024-11 (10 rows), 2026-05 (1 row)</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr"/>
+          <t>A difference of -0.175 refused_items in the average month, latest 12 months against the 12 before, over 3,272 rows, but some of its monthly averages in the two compared windows are at or below zero (they cross zero), so a percentage change, and a percentage bar, have no meaning for it, so no change test was run. Worth watching; not yet a confirmed change.</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>No change test is available for this measure: some of its monthly averages in the two compared windows are at or below zero (they cross zero), so a percentage change, and a percentage bar, have no meaning for it. It would need a materiality bar in the measure's own units, which this release does not take, so it can be watched but not confirmed.</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>26.41330166270784</v>
+        <v>-0.175094905751932</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1950s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT (SELECT AVG(v) FROM (SELECT AVG("refused_items") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2025-09' AND '2026-08' GROUP BY _month HAVING COUNT("refused_items") &gt;= 15)) - (SELECT AVG(v) FROM (SELECT AVG("refused_items") AS v FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE "refused_items" IS NOT NULL AND _month BETWEEN '2024-09' AND '2025-08' GROUP BY _month HAVING COUNT("refused_items") &gt;= 15))</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>measure.decade_built.share.3</t>
+          <t>measure.ward_name.share.1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5974,11 +5978,11 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where decade_built is '1970s' (rank 3 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where ward_name is 'Toronto-St. Paul's' (rank 1 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>13.98258115597783</v>
+        <v>9.675376088677751</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -6014,18 +6018,18 @@
         <v>1</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>13.98258115597783</v>
+        <v>9.675376088677751</v>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1970s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Toronto-St. Paul''s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>measure.decade_built.share.4</t>
+          <t>measure.ward_name.share.2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -6035,11 +6039,11 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where decade_built is '1980s' (rank 4 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where ward_name is 'Etobicoke-Lakeshore' (rank 2 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4.386381631037213</v>
+        <v>6.967537608867775</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -6075,18 +6079,18 @@
         <v>1</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>4.386381631037213</v>
+        <v>6.967537608867775</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1980s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Etobicoke-Lakeshore' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>measure.decade_built.share.5</t>
+          <t>measure.ward_name.share.3</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -6096,11 +6100,11 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where decade_built is '1920s' (rank 5 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where ward_name is 'York South-Weston' (rank 3 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4.180522565320665</v>
+        <v>6.951702296120349</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -6136,18 +6140,18 @@
         <v>1</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>4.180522565320665</v>
+        <v>6.951702296120349</v>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1920s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'York South-Weston' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>measure.storeys_band.share.1</t>
+          <t>measure.ward_name.share.4</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -6157,11 +6161,11 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where storeys_band is '3-4' (rank 1 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where ward_name is 'Eglinton-Lawrence' (rank 4 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>51.06888361045131</v>
+        <v>6.920031670625495</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -6197,18 +6201,18 @@
         <v>1</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>51.06888361045131</v>
+        <v>6.920031670625495</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '3-4' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'Eglinton-Lawrence' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>measure.storeys_band.share.2</t>
+          <t>measure.ward_name.share.5</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -6218,11 +6222,11 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where storeys_band is '5-9' (rank 2 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where ward_name is 'York Centre' (rank 5 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>22.67616785431512</v>
+        <v>6.619160728424387</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -6258,18 +6262,18 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>22.67616785431512</v>
+        <v>6.619160728424387</v>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '5-9' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "ward_name" = 'York Centre' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>measure.storeys_band.share.3</t>
+          <t>measure.district.share.1</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6279,11 +6283,11 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where storeys_band is '10-19' (rank 3 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where district is 'Toronto and East York' (rank 1 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>19.61995249406176</v>
+        <v>39.74663499604117</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -6319,18 +6323,18 @@
         <v>1</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>19.61995249406176</v>
+        <v>39.74663499604117</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '10-19' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Toronto and East York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>measure.storeys_band.share.4</t>
+          <t>measure.district.share.2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6340,11 +6344,11 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Share of rows where storeys_band is '20+' (rank 4 by rows), 2023-06 to 2026-08</t>
+          <t>Share of rows where district is 'North York' (rank 2 by rows), 2023-06 to 2026-08</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.634996041171813</v>
+        <v>25.68487727632621</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -6380,880 +6384,872 @@
         <v>1</v>
       </c>
       <c r="P95" s="2" t="n">
+        <v>25.68487727632621</v>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'North York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>measure.district.share.3</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where district is 'Etobicoke York' (rank 3 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>22.18527315914489</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>22.18527315914489</v>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Etobicoke York' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>measure.district.share.4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where district is 'Scarborough' (rank 4 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>12.38321456848773</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>12.38321456848773</v>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "district" = 'Scarborough' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>measure.property_type.share.1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where property_type is 'PRIVATE' (rank 1 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>84.3230403800475</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>84.3230403800475</v>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'PRIVATE' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>measure.property_type.share.2</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where property_type is 'TCHC' (rank 2 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>9.105304829770388</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>9.105304829770388</v>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'TCHC' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>measure.property_type.share.3</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where property_type is 'SOCIAL HOUSING' (rank 3 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>6.571654790182106</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>6.571654790182106</v>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "property_type" = 'SOCIAL HOUSING' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>measure.decade_built.share.1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where decade_built is '1960s' (rank 1 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>33.34916864608076</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>33.34916864608076</v>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1960s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>measure.decade_built.share.2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where decade_built is '1950s' (rank 2 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>26.41330166270784</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>26.41330166270784</v>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1950s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>measure.decade_built.share.3</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where decade_built is '1970s' (rank 3 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>13.98258115597783</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>13.98258115597783</v>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1970s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>measure.decade_built.share.4</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where decade_built is '1980s' (rank 4 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>4.386381631037213</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>4.386381631037213</v>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1980s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>measure.decade_built.share.5</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where decade_built is '1920s' (rank 5 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>4.180522565320665</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>4.180522565320665</v>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "decade_built" = '1920s' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>measure.storeys_band.share.1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where storeys_band is '3-4' (rank 1 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>51.06888361045131</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>51.06888361045131</v>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '3-4' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>measure.storeys_band.share.2</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where storeys_band is '5-9' (rank 2 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>22.67616785431512</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>22.67616785431512</v>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '5-9' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>measure.storeys_band.share.3</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where storeys_band is '10-19' (rank 3 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>19.61995249406176</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>19.61995249406176</v>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '10-19' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>measure.storeys_band.share.4</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Share of rows where storeys_band is '20+' (rank 4 by rows), 2023-06 to 2026-08</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
         <v>6.634996041171813</v>
       </c>
-      <c r="Q95" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>6681</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>A background measurement that describes the data or supports a finding; it is not advice on its own.</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>6.634996041171813</v>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
         <is>
           <t>SELECT 100.0 * SUM(CASE WHEN "storeys_band" = '20+' THEN 1 ELSE 0 END) / COUNT(*) FROM "_northledger_measure_client_rentsafeto_evaluation_view" WHERE _month BETWEEN '2023-06' AND '2026-08'</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.next</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>Forecast of monthly rows in RentSafeTO-evaluation-view.csv for 2026-09</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>934.2711699185875</v>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>method: a damped trend fitted on the log scale (Holt), chosen as the lowest error when the last 7 months were replayed; horizon shortened to 1 month(s): a longer one would leave fewer than 12 backtest months with a band; the series has never been below zero, so forecasts and 80% ranges below zero were set to zero; rows dated after 2026-08 are left out: the last month in the file (2026-09) holds the analysis date 2026-09-23, so it is not over yet</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>The method could only be replayed over 7 months, fewer than the 12 we require to judge it.</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
-          <t>A longer history, so at least 12 months can be held out.</t>
-        </is>
-      </c>
-      <c r="O96" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>934.2711699185875</v>
-      </c>
-      <c r="Q96" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "forward.point@1"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.next.lo80</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Low end of the 80% range for monthly rows in RentSafeTO-evaluation-view.csv in 2026-09</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>669.3227587370277</v>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr"/>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P97" s="3" t="n">
-        <v>669.3227587370277</v>
-      </c>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "forward.lo80@1"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.next.hi80</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>High end of the 80% range for monthly rows in RentSafeTO-evaluation-view.csv in 2026-09</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>1094.670106468701</v>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K98" s="3" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr"/>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr"/>
-      <c r="O98" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P98" s="3" t="n">
-        <v>1094.670106468701</v>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "forward.hi80@1"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.backtest.months</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>Months replayed to choose and check the method (each forecast made from what was known at the time)</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J99" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr"/>
-      <c r="O99" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "holdout"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.history.months</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Months of history the forecast learned from</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr"/>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr"/>
-      <c r="O100" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P100" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "history_months"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.backtest.mape</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>Average miss of the chosen method when the last 7 months were replayed, as a share of the actual value</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>68.54440191573374</v>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J101" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr"/>
-      <c r="O101" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P101" s="3" t="n">
-        <v>68.54440191573374</v>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "champion.mape"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.backtest.mape_h1</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>Average miss of the chosen method one month ahead, when the last 7 months were replayed</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>68.54440191573374</v>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K102" s="3" t="inlineStr"/>
-      <c r="L102" s="3" t="inlineStr"/>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr"/>
-      <c r="O102" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>68.54440191573374</v>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "champion.mape_h1"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.backtest.mase</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>Error of the chosen method relative to the same-month-last-year rule's typical miss (MASE)</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>0.4549469415847761</v>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P103" s="3" t="n">
-        <v>0.4549469415847761</v>
-      </c>
-      <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "champion.mase"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.naive.mase</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>Replay error (MASE) of the method: repeat last month's value</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>0.7384496423738643</v>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K104" s="3" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr"/>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr"/>
-      <c r="O104" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P104" s="3" t="n">
-        <v>0.7384496423738643</v>
-      </c>
-      <c r="Q104" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.naive.mase"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.naive.mape</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>Replay average miss of the method: repeat last month's value</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>78.38751323574397</v>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr"/>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="inlineStr"/>
-      <c r="O105" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P105" s="3" t="n">
-        <v>78.38751323574397</v>
-      </c>
-      <c r="Q105" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.naive.mape"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.seasonal_naive.mase</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>Replay error (MASE) of the method: repeat the same month from last year</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>0.6031316450802243</v>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K106" s="3" t="inlineStr"/>
-      <c r="L106" s="3" t="inlineStr"/>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr"/>
-      <c r="O106" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P106" s="3" t="n">
-        <v>0.6031316450802243</v>
-      </c>
-      <c r="Q106" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.seasonal_naive.mase"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.seasonal_naive.mape</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>Replay average miss of the method: repeat the same month from last year</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>68.13530535790839</v>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K107" s="3" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P107" s="3" t="n">
-        <v>68.13530535790839</v>
-      </c>
-      <c r="Q107" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.seasonal_naive.mape"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.drift.mase</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>Replay error (MASE) of the method: extend the straight line from the first month to the last</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>0.7402260176279121</v>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J108" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K108" s="3" t="inlineStr"/>
-      <c r="L108" s="3" t="inlineStr"/>
-      <c r="M108" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N108" s="3" t="inlineStr"/>
-      <c r="O108" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P108" s="3" t="n">
-        <v>0.7402260176279121</v>
-      </c>
-      <c r="Q108" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.drift.mase"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>forecast.monthly_rows.model.drift.mape</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>Replay average miss of the method: extend the straight line from the first month to the last</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>78.81669532853013</v>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>RentSafeTO-evaluation-view.csv</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>6315</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="3" t="inlineStr">
-        <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P109" s="3" t="n">
-        <v>78.81669532853013</v>
-      </c>
-      <c r="Q109" s="3" t="inlineStr">
-        <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.drift.mape"}</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.model.loglinear_season.mase</t>
+          <t>forecast.monthly_rows.next</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7263,15 +7259,15 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Replay error (MASE) of the method: a log-linear trend with month-of-year effects</t>
+          <t>Forecast of monthly rows in RentSafeTO-evaluation-view.csv for 2026-09</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.789378201617588</v>
+        <v>934.2711699185875</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -7292,29 +7288,37 @@
         <v>93.90000000000001</v>
       </c>
       <c r="K110" s="3" t="inlineStr"/>
-      <c r="L110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>method: a damped trend fitted on the log scale (Holt), chosen as the lowest error when the last 6 months were replayed; horizon shortened to 1 month(s): a longer one would leave fewer than 12 backtest months with a band; the average miss is not stated as a share of the actual value: a replayed month was zero or under 10% of the typical month, where a percentage miss is undefined or explodes; MASE carries the error instead; the series has never been below zero, so forecasts and 80% ranges below zero were set to zero; rows dated after 2026-08 are left out: the last month in the file (2026-09) holds the analysis date 2026-09-23, so it is not over yet; the 80% range is for each month on its own, not for the whole path of months together; the method was chosen on its average absolute miss, so the forecast is a middle value (about as likely to be under as over), not an average; replay error (MASE, the headline measure): 0.56, the method's average miss divided by the typical miss of repeating the same month from last year in the history before the replay (below 1 means smaller than that typical miss). Over the same replayed months it removed 24% of that rule's own error. Its miss is not stated as a share of the actual value: a replayed month was zero or under 10% of the typical month, where a percentage miss is undefined or explodes; the 80% range for 2026-09: about 80% of months land in ranges built this way, on average across businesses like this (measured: 84% to 90% on simulated steady series). With only 15 past errors behind it, this particular range could be somewhat wider or narrower in truth: typically between 76% and 97%</t>
+        </is>
+      </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
-        </is>
-      </c>
-      <c r="N110" s="3" t="inlineStr"/>
+          <t>The method could only be replayed over 6 months, fewer than the 12 we require to judge it.</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>A longer history, so at least 12 months can be held out.</t>
+        </is>
+      </c>
       <c r="O110" s="3" t="b">
         <v>1</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0.789378201617588</v>
+        <v>934.2711699185875</v>
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.loglinear_season.mase"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.point@1"}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.model.loglinear_season.mape</t>
+          <t>forecast.monthly_rows.next.lo80</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7324,15 +7328,15 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Replay average miss of the method: a log-linear trend with month-of-year effects</t>
+          <t>Low end of the 80% range for monthly rows in RentSafeTO-evaluation-view.csv in 2026-09</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>117.7464684093541</v>
+        <v>507.7372871174978</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -7364,18 +7368,18 @@
         <v>1</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>117.7464684093541</v>
+        <v>507.7372871174978</v>
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "model.loglinear_season.mape"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.lo80@1"}</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.coverage.hits</t>
+          <t>forecast.monthly_rows.next.hi80</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7385,15 +7389,15 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Replayed months whose actual value fell inside the month-ahead 80% range</t>
+          <t>High end of the 80% range for monthly rows in RentSafeTO-evaluation-view.csv in 2026-09</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>6</v>
+        <v>1323.453877344699</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -7425,18 +7429,18 @@
         <v>1</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>6</v>
+        <v>1323.453877344699</v>
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "coverage.hits"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.hi80@1"}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.coverage.n</t>
+          <t>forecast.monthly_rows.backtest.months</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7446,15 +7450,15 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Replayed months with a month-ahead 80% range built only from errors known at the time</t>
+          <t>Months replayed to choose and check the method (each forecast made from what was known at the time)</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>months</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -7486,18 +7490,18 @@
         <v>1</v>
       </c>
       <c r="P113" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "coverage.n"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "holdout"}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.coverage_all.hits</t>
+          <t>forecast.monthly_rows.history.months</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7507,15 +7511,15 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Replayed forecasts at every horizon whose actual value fell inside the 80% range (overlapping checks)</t>
+          <t>Months of history the forecast learned from</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>months</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -7547,18 +7551,18 @@
         <v>1</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "coverage.all_hits"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "history_months"}</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>forecast.monthly_rows.coverage_all.n</t>
+          <t>forecast.monthly_rows.baseline_test.months</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -7568,11 +7572,11 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Replayed forecasts at every horizon with an 80% range built only from errors known at the time (overlapping checks)</t>
+          <t>Replayed months on which the method's month-ahead forecast (its model picked at each month from what was known then) was compared with repeating the same month from last year</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -7608,16 +7612,2696 @@
         <v>1</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>{"config": {"band": 0.8, "horizon": 12, "loglinear_window": 60, "max_history": 120, "max_holdout": 24, "min_band_errors": 8, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0}, "fill": "zero", "holdout_window": ["2026-02", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.45494694158477605, "coverage_hits": 6, "coverage_n": 7, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "history_months": 39, "holdout": 7, "horizon": 1, "seasonal_naive_mase": 0.6031316450802243, "start": "2023-06"}, "target": "coverage.all_n"}</t>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.n"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.baseline_test.gain</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Share of the same-month-last-year rule's month-ahead replay miss that the method removed, picking its model at each month from what was known then (below 0 means it did worse)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>-0.3077763528122752</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr"/>
+      <c r="O116" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P116" s="3" t="n">
+        <v>-0.3077763528122752</v>
+      </c>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.gain"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.baseline_test.p</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>If the method were no more accurate one month ahead than repeating the same month from last year, the chance of a replay gain at least this large (one-sided Diebold-Mariano test with the small-sample correction)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0.6390383392033039</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr"/>
+      <c r="O117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P117" s="3" t="n">
+        <v>0.6390383392033039</v>
+      </c>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.p"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.backtest.mase</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Error of the chosen method relative to the same-month-last-year rule's typical miss (MASE)</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0.5573100034413506</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr"/>
+      <c r="O118" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P118" s="3" t="n">
+        <v>0.5573100034413506</v>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "champion.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.backtest.skill</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Share of the same-month-last-year rule's replay error that the chosen method removed (1 - MASE ratio; below 0 means it did worse)</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0.2456921381993441</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr"/>
+      <c r="O119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P119" s="3" t="n">
+        <v>0.2456921381993441</v>
+      </c>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "champion.skill_vs_sn"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.backtest.msis</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Interval score of the chosen method's replayed 80% ranges, scaled like MASE (width plus a penalty for each miss; lower is better)</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>4.129921295589512</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr"/>
+      <c r="O120" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P120" s="3" t="n">
+        <v>4.129921295589512</v>
+      </c>
+      <c r="Q120" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "sharpness.champion_msis"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.backtest.msis_seasonal_naive</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Interval score of the same kind of 80% range around the same-month-last-year rule, on the same replayed months</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>5.460746566560334</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr"/>
+      <c r="O121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P121" s="3" t="n">
+        <v>5.460746566560334</v>
+      </c>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "sharpness.seasonal_naive_msis"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.model.naive.mase</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: repeat last month's value</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0.9046008119079838</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr"/>
+      <c r="O122" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P122" s="3" t="n">
+        <v>0.9046008119079838</v>
+      </c>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.naive.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.model.seasonal_naive.mase</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: repeat the same month from last year</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0.7388362652232747</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr"/>
+      <c r="O123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P123" s="3" t="n">
+        <v>0.7388362652232747</v>
+      </c>
+      <c r="Q123" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.seasonal_naive.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.model.drift.mase</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: extend the straight line from the first month to the last</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0.9067768715941923</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr"/>
+      <c r="O124" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P124" s="3" t="n">
+        <v>0.9067768715941923</v>
+      </c>
+      <c r="Q124" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.drift.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.model.loglinear_season.mase</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: a log-linear trend with month-of-year effects</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0.966232596259137</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr"/>
+      <c r="O125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>0.966232596259137</v>
+      </c>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.loglinear_season.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.next.band_errors</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Past errors the 80% range for 2026-09 is built from</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr"/>
+      <c r="O126" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P126" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.n_errors@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.next.band_cov_p10</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Low end (10th percentile) of the share of months the 80% range for 2026-09 may truly cover, given how few errors it rests on</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0.7644311459821438</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr"/>
+      <c r="O127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P127" s="3" t="n">
+        <v>0.7644311459821438</v>
+      </c>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.coverage_p10@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.next.band_cov_p90</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>High end (90th percentile) of the share of months the 80% range for 2026-09 may truly cover, given how few errors it rests on</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.9639630074993875</v>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr"/>
+      <c r="O128" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>0.9639630074993875</v>
+      </c>
+      <c r="Q128" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.coverage_p90@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.next.band_max_level</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Highest coverage any range built from that many errors can reach</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P129" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.max_level@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.coverage.hits</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Replayed months whose actual value fell inside the month-ahead 80% range</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr"/>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.hits"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.coverage.n</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Replayed months with a month-ahead 80% range built only from errors known at the time</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr"/>
+      <c r="O131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P131" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.n"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.coverage.binomial_p</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>If the month-ahead 80% range truly held 80% of the time, the chance of a replay record at least this far from it (exact binomial test)</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.6067840000000007</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr"/>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr"/>
+      <c r="O132" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>0.6067840000000007</v>
+      </c>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.binomial_p"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.coverage_all.hits</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Replayed forecasts at every horizon whose actual value fell inside the 80% range (overlapping checks)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr"/>
+      <c r="O133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.all_hits"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>forecast.monthly_rows.coverage_all.n</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Replayed forecasts at every horizon with an 80% range built only from errors known at the time (overlapping checks)</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr"/>
+      <c r="O134" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "holt_damped_log", "params": {"alpha": 0.9, "beta": 0.2, "phi": 0.8, "transform": "log1p"}, "seed": 0, "series_sql": "SELECT _month, COUNT(*) FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": -0.3077763528122752, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.6390383392033039, "baseline_won": false, "beats_seasonal_naive": true, "champion": "holt_damped_log", "champion_mase": 0.5573100034413506, "champion_msis": 4.129921295589512, "champion_skill_vs_sn": 0.2456921381993441, "christoffersen_cc_p": null, "christoffersen_ind_p": null, "coverage_binomial_p": 0.6067840000000007, "coverage_hits": 6, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 0.7388362652232747, "seasonal_naive_msis": 5.460746566560334, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.all_n"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Forecast of monthly total refused_items in RentSafeTO-evaluation-view.csv for 2026-09</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>164.0526315789474</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>method: extend the straight line from the first month to the last, chosen as the lowest error when the last 6 months were replayed; horizon shortened to 1 month(s): a longer one would leave fewer than 12 backtest months with a band; the average miss is not stated as a share of the actual value: a replayed month was zero or under 10% of the typical month, where a percentage miss is undefined or explodes; MASE carries the error instead; the series has never been below zero, so forecasts and 80% ranges below zero were set to zero; rows dated after 2026-08 are left out: the last month in the file (2026-09) holds the analysis date 2026-09-23, so it is not over yet; the 80% range is for each month on its own, not for the whole path of months together; the method was chosen on its average absolute miss, so the forecast is a middle value (about as likely to be under as over), not an average; replay error (MASE, the headline measure): 0.78, the method's average miss divided by the typical miss of repeating the same month from last year in the history before the replay (below 1 means smaller than that typical miss). Over the same replayed months it removed 44% of that rule's own error. Its miss is not stated as a share of the actual value: a replayed month was zero or under 10% of the typical month, where a percentage miss is undefined or explodes; the 80% range for 2026-09: about 80% of months land in ranges built this way, on average across businesses like this (measured: 84% to 90% on simulated steady series). With only 15 past errors behind it, this particular range could be somewhat wider or narrower in truth: typically between 76% and 97%</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>The method could only be replayed over 6 months, fewer than the 12 we require to judge it.</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>A longer history, so at least 12 months can be held out.</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P135" s="3" t="n">
+        <v>164.0526315789474</v>
+      </c>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.point@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.lo80</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Low end of the 80% range for monthly total refused_items in RentSafeTO-evaluation-view.csv in 2026-09</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>113.0526315789474</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr"/>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr"/>
+      <c r="O136" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>113.0526315789474</v>
+      </c>
+      <c r="Q136" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.lo80@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.hi80</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>High end of the 80% range for monthly total refused_items in RentSafeTO-evaluation-view.csv in 2026-09</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>285.8304093567251</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr"/>
+      <c r="O137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P137" s="3" t="n">
+        <v>285.8304093567251</v>
+      </c>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.hi80@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.backtest.months</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Months replayed to choose and check the method (each forecast made from what was known at the time)</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K138" s="3" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr"/>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr"/>
+      <c r="O138" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P138" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q138" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "holdout"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.history.months</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Months of history the forecast learned from</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr"/>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr"/>
+      <c r="O139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P139" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "history_months"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.baseline_test.months</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Replayed months on which the method's month-ahead forecast (its model picked at each month from what was known then) was compared with repeating the same month from last year</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K140" s="3" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr"/>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr"/>
+      <c r="O140" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P140" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q140" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.n"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.baseline_test.gain</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Share of the same-month-last-year rule's month-ahead replay miss that the method removed, picking its model at each month from what was known then (below 0 means it did worse)</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0.4431319431319432</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr"/>
+      <c r="O141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P141" s="3" t="n">
+        <v>0.4431319431319432</v>
+      </c>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.gain"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.baseline_test.p</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>If the method were no more accurate one month ahead than repeating the same month from last year, the chance of a replay gain at least this large (one-sided Diebold-Mariano test with the small-sample correction)</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0.1853537515458124</v>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K142" s="3" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr"/>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr"/>
+      <c r="O142" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P142" s="3" t="n">
+        <v>0.1853537515458124</v>
+      </c>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "baseline_test.p"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.backtest.mase</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Error of the chosen method relative to the same-month-last-year rule's typical miss (MASE)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0.775278059700869</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K143" s="3" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr"/>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr"/>
+      <c r="O143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P143" s="3" t="n">
+        <v>0.775278059700869</v>
+      </c>
+      <c r="Q143" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "champion.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.backtest.skill</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Share of the same-month-last-year rule's replay error that the chosen method removed (1 - MASE ratio; below 0 means it did worse)</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0.4431319431319432</v>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K144" s="3" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr"/>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr"/>
+      <c r="O144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P144" s="3" t="n">
+        <v>0.4431319431319432</v>
+      </c>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "champion.skill_vs_sn"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.backtest.msis</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Interval score of the chosen method's replayed 80% ranges, scaled like MASE (width plus a penalty for each miss; lower is better)</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>6.358360377066913</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K145" s="3" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr"/>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr"/>
+      <c r="O145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P145" s="3" t="n">
+        <v>6.358360377066913</v>
+      </c>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "sharpness.champion_msis"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.backtest.msis_seasonal_naive</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Interval score of the same kind of 80% range around the same-month-last-year rule, on the same replayed months</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>6.498447312183121</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K146" s="3" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr"/>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr"/>
+      <c r="O146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P146" s="3" t="n">
+        <v>6.498447312183121</v>
+      </c>
+      <c r="Q146" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "sharpness.seasonal_naive_msis"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.model.naive.mase</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: repeat last month's value</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0.7837273991655076</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K147" s="3" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr"/>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr"/>
+      <c r="O147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P147" s="3" t="n">
+        <v>0.7837273991655076</v>
+      </c>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.naive.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.model.seasonal_naive.mase</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: repeat the same month from last year</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>1.39221140472879</v>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K148" s="3" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr"/>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr"/>
+      <c r="O148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P148" s="3" t="n">
+        <v>1.39221140472879</v>
+      </c>
+      <c r="Q148" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.seasonal_naive.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.model.holt_damped_log.mase</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: a damped trend fitted on the log scale (Holt)</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0.9282764800180294</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K149" s="3" t="inlineStr"/>
+      <c r="L149" s="3" t="inlineStr"/>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr"/>
+      <c r="O149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P149" s="3" t="n">
+        <v>0.9282764800180294</v>
+      </c>
+      <c r="Q149" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.holt_damped_log.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.model.loglinear_season.mase</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Replay error (MASE) of the method: a log-linear trend with month-of-year effects</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>1.34665989771559</v>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K150" s="3" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr"/>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr"/>
+      <c r="O150" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P150" s="3" t="n">
+        <v>1.34665989771559</v>
+      </c>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "model.loglinear_season.mase"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.band_errors</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Past errors the 80% range for 2026-09 is built from</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K151" s="3" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr"/>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr"/>
+      <c r="O151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P151" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q151" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.n_errors@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.band_cov_p10</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Low end (10th percentile) of the share of months the 80% range for 2026-09 may truly cover, given how few errors it rests on</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0.7644311459821438</v>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K152" s="3" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr"/>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr"/>
+      <c r="O152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P152" s="3" t="n">
+        <v>0.7644311459821438</v>
+      </c>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.coverage_p10@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.band_cov_p90</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>High end (90th percentile) of the share of months the 80% range for 2026-09 may truly cover, given how few errors it rests on</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0.9639630074993875</v>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K153" s="3" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr"/>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr"/>
+      <c r="O153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>0.9639630074993875</v>
+      </c>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.coverage_p90@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.next.band_max_level</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Highest coverage any range built from that many errors can reach</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K154" s="3" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr"/>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr"/>
+      <c r="O154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P154" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "forward.max_level@1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.coverage.hits</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Replayed months whose actual value fell inside the month-ahead 80% range</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr"/>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr"/>
+      <c r="O155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q155" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.hits"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.coverage.n</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Replayed months with a month-ahead 80% range built only from errors known at the time</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K156" s="3" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr"/>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr"/>
+      <c r="O156" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P156" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.n"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.coverage.binomial_p</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>If the month-ahead 80% range truly held 80% of the time, the chance of a replay record at least this far from it (exact binomial test)</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0.3446400000000005</v>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K157" s="3" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr"/>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr"/>
+      <c r="O157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P157" s="3" t="n">
+        <v>0.3446400000000005</v>
+      </c>
+      <c r="Q157" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.binomial_p"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.coverage_all.hits</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Replayed forecasts at every horizon whose actual value fell inside the 80% range (overlapping checks)</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K158" s="3" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr"/>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr"/>
+      <c r="O158" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P158" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.all_hits"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>forecast.total_refused_items.coverage_all.n</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Replayed forecasts at every horizon with an 80% range built only from errors known at the time (overlapping checks)</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>RentSafeTO-evaluation-view.csv</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K159" s="3" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr"/>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>A detail of the forecast it belongs to (its range, its replay record); judged with that forecast, not on its own.</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr"/>
+      <c r="O159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P159" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>{"config": {"band": 0.8, "band_dependence": "ar1_widen", "band_errors": "envelope", "band_method": "conformal_rank", "baseline_test_min_known": 12, "fit_from": null, "horizon": 12, "loglinear_window": 60, "mape_min_share": 0.1, "max_history": 120, "max_holdout": 24, "min_band_errors": 9, "min_holdout": 12, "min_train": 24, "nonnegative": "auto", "seed": 0, "step_month": null, "useful_range_ratio": 2.0}, "fill": "zero", "holdout_window": ["2026-03", "2026-08"], "kind": "northledger.forecast/1", "model": "drift", "params": {"slope": 3.0526315789473686}, "seed": 0, "series_sql": "SELECT _month, SUM(\"refused_items\") FROM \"_northledger_measure_client_rentsafeto_evaluation_view\" WHERE \"refused_items\" IS NOT NULL AND _month BETWEEN '2023-06' AND '2026-08' GROUP BY _month ORDER BY _month", "summary": {"as_of": "2026-09-23", "band_coverage_p10_p90_h1": [0.7644311459821438, 0.9639630074993875], "band_dependence": "ar1_widen", "band_h1": true, "band_level": 0.8, "band_max_level_h1": 0.875, "band_method": "conformal_rank", "band_n_effective_h1": 15.0, "band_n_errors_h1": 15, "band_scope": "per_month", "band_widened_by_max": 1.0, "baseline_test_gain": 0.44313194313194315, "baseline_test_method": "dm_hln_nested_h1", "baseline_test_n": 6, "baseline_test_p": 0.18535375154581235, "baseline_won": false, "beats_seasonal_naive": true, "champion": "drift", "champion_mase": 0.775278059700869, "champion_msis": 6.358360377066913, "champion_skill_vs_sn": 0.44313194313194315, "christoffersen_cc_p": 0.6965703475199998, "christoffersen_ind_p": 0.7098338753206082, "coverage_binomial_p": 0.3446400000000005, "coverage_hits": 4, "coverage_n": 6, "end": "2026-08", "error_mode": "additive", "first_forecast_month": "2026-09", "headline_error": "mase", "history_months": 39, "holdout": 6, "horizon": 1, "mape_suppressed": true, "seasonal_naive_mase": 1.39221140472879, "seasonal_naive_msis": 6.498447312183121, "start": "2023-06", "step_months": [], "step_straddled": 0}, "target": "coverage.all_n"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q115"/>
+  <autoFilter ref="A1:Q159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>